--- a/Behaviour/BCIO-behaviour-hierarchy.xlsx
+++ b/Behaviour/BCIO-behaviour-hierarchy.xlsx
@@ -446,14 +446,14 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
           <t>Examples</t>
@@ -461,24 +461,24 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Comment</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BCIO:050435</t>
+          <t>BCIO:036107</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>behavioural attribute</t>
+          <t>process aggregate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -490,7 +490,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A process attribute of an individual human behaviour.</t>
+          <t>An occurrent consisting exactly of a plurality of processes that are process_aggregate_member_parts_of that occurrent for all times at which it exists.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -498,22 +498,22 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>An attribute of a behaviour.</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Processes that repeat over time.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCIO:050431</t>
+          <t>BCIO:050267</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mental exertion expended on a behaviour</t>
+          <t>uniform process aggregate</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -524,7 +524,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the level of mental effort expended on the behaviour to be enacted.</t>
+          <t>A process aggregate whose member parts are of the same type.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -532,23 +532,23 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>The mental effort required to perform a behaviour.</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Several processes of the same type repeated over time.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCIO:050433</t>
+          <t>BCIO:050448</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognitive exertion expended on a behaviour</t>
+          <t>population behaviour pattern</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -558,41 +558,36 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mental exertion expended on a behaviour where the exertion involves cognitive processes.</t>
+          <t>A uniform process aggregate whose members are individual behaviour patterns of a population.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>The effort relating to thinking required to perform a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIO:050466</t>
+          <t>BCIO:036100</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>low cognitive exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>individual human behaviour pattern</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cognitive exertion expended on a behaviour that is low.</t>
+          <t>A uniform process aggregate whose member parts are behaviours of the same type and in the same person.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -600,16 +595,27 @@
           <t>behaviour</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Individual human behaviours of the same type repeated over time.</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Low cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
+          <t>behaviour pattern</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>The term 'pattern' is used to refer to several processes (individual human behaviours) of the same type being repeated overtime.
+This class is intended to include behaviours that can usefully be characterised in terms of frequency and pattern of enactment with a temporal start and end of the series. This means that the series can be terminated (e.g. stopping smoking), interrupted (e.g. abstaining from alcohol consumption for a month), and changed in frequency (e.g. cutting down on snacks).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:050462</t>
+          <t>BCIO:050210</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -617,7 +623,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>high cognitive exertion expended on a behaviour</t>
+          <t>consumption behaviour pattern</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -626,75 +632,65 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cognitive exertion expended on a behaviour that is high.</t>
+          <t>An individual human behaviour pattern that involves consumption behaviour.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>High cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:050470</t>
+          <t>BCIO:050211</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>moderate cognitive exertion expended on a behaviour</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>substance use behaviour pattern</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cognitive exertion expended on a behaviour that is medium.</t>
+          <t>A consumption behaviour pattern that involves substance use behaviour.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Moderate cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050472</t>
+          <t>BCIO:036102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>moderate mental exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tobacco use behaviour pattern</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mental exertion expended on a behaviour that is medium.</t>
+          <t>A substance use behaviour pattern that involves tobacco use.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -704,99 +700,84 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Moderate mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+          <t>tobacco use</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050468</t>
+          <t>BCIO:036104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>low mental exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>tobacco smoking behaviour pattern</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mental exertion expended on a behaviour that is low.</t>
+          <t>A tobacco use behaviour pattern that involves tobacco smoking behaviour.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Low mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050464</t>
+          <t>BCIO:036106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>high mental exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>cigarette smoking behaviour pattern</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mental exertion expended on a behaviour that is high.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>High mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
+          <t>A tobacco smoking behaviour pattern that involves cigarette smoking behaviour.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050434</t>
+          <t>BCIO:050805</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>emotional management exertion expended on a behaviour</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>behaviour pattern maintenance</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mental exertion expended on a behaviour where the exertion involves control over emotions or their expression.</t>
+          <t>An individual human behaviour pattern that is continued.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -804,33 +785,33 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>The effort a person has to exert to manage their emotions when performing a behaviour.</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Behaviour is continued even if there are historical or current barriers to doing so.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050467</t>
+          <t>BCIO:050804</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>behaviour chain</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>low emotional management exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emotional management exertion expended on a behaviour that is low.</t>
+          <t>A process aggregate whose members are behaviours causally linked to each other in a sequence.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -838,92 +819,82 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Low emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A behaviour chain can involve different behaviours, whereas a behaviour pattern can involve the same behaviour. Patterns are not necessarily causally linked.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050463</t>
+          <t>BCIO:034000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>population behaviour</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>high emotional management exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emotional management exertion expended on a behaviour that is high.</t>
+          <t>An aggregate of individual human behaviours of members of a population.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>High emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050471</t>
+          <t>BCIO:050808</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>moderate emotional management exertion expended on a behaviour</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>collective behaviour</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Emotional management exertion expended on a behaviour that is medium.</t>
+          <t>A population behaviour that is aimed at achieving a goal shared by members of that population.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Moderate emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050444</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>behavioural reflectiveness</t>
-        </is>
-      </c>
+          <t>BFO:0000034</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -932,38 +903,28 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the degree to which the behaviour is under the control of reflective motivation.</t>
+          <t>A disposition that exists in virtue of the bearer’s physical make-up and this physical make-up is something the bearer possesses because it came into being, either through evolution (in the case of natural biological entities) or through intentional design (in the case of artifacts), in order to realize processes of a certain sort. (axiom label in BFO2 Reference: [064-001])</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>How far a behaviour is enacted after thinking about it and its consequences.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>This class is a dimension and involves any conscious thought processes that lead to a behaviour in some way, even if those processes are themselves influenced by emotional processes and biases.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050833</t>
+          <t>BCIO:036001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>reflectively controlled</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>human life function</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -971,27 +932,33 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Behavioural reflectiveness in which the behaviour is predominantly controlled by reflective motivation.</t>
+          <t>A function that inheres in a human being and is realised in processes that enable the human to survive and thrive.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>There are complex sets of processes involved in the realisation of human life functions, only some which would behaviours. An example for a human life function that is not a behaviour function: human thermoregulation via sweating function. However, some behaviours can fulfil 'human life functions'.
+The term 'survive' refers to continuing one's existence (e.g., staying alive), while 'thrive' includes a wide range of processes that improve an animal's life, including physical and mental wellbeing and experiencing positive social interactions, as well as being able to reproduce. Many processes can contribute to a human surviving and thriving.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050430</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>behavioural form</t>
-        </is>
-      </c>
+          <t>BCIO:050428</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>behavioural frequency</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1000,7 +967,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the physical way in which a behaviour is enacted.</t>
+          <t>A data item that is about the number of times a behaviour occurs in a time period.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1008,24 +975,24 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The way in which the behaviour is performed, including the shape of one’s muscles and skeletal alignment during the behaviour. </t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>The number of times a person performs a behaviour within a specific period.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050822</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>identity congruence</t>
-        </is>
-      </c>
+          <t>BCIO:050429</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>number of behavioural occurrences</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1034,27 +1001,32 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the extent to which one’s behaviour is believed to be consistent with one’s core, positive self-identity.</t>
+          <t>A data item that is about the number of times a behaviour has occurred.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of times a person performs a behaviour. </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050432</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>physical exertion expended on a behaviour</t>
-        </is>
-      </c>
+          <t>BCIO:050300</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1063,33 +1035,33 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the level of musculoskeletal work expended on the behaviour to be enacted.</t>
+          <t>A specifically dependent continuant that inheres in a person.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>The physical effort required to perform a behaviour.</t>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050469</t>
+          <t>BCIO:050451</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>low physical exertion expended on behaviour</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>abstinence from a behaviour</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1097,7 +1069,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Physical exertion expended on a behaviour that is low.</t>
+          <t>A personal attribute in which a person does not engage in a behaviour during a time period.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1105,25 +1077,25 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means </t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Not performing a behaviour for some period of time.1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050473</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>BCIO:050435</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>behavioural attribute</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>moderate physical exertion expended on behaviour</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1131,7 +1103,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Physical exertion expended on a behaviour that is medium.</t>
+          <t>A process attribute of an individual human behaviour.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1139,25 +1111,25 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Moderate physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>An attribute of a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050465</t>
+          <t>BCIO:050835</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>high physical exertion expended on behaviour</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>response cost</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1165,30 +1137,25 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Physical exertion expended on a behaviour that is high</t>
+          <t>A behavioural attribute that is the time, effort, financial cost, or aversiveness of enacting a behaviour.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>High physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050835</t>
+          <t>BCIO:050431</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>response cost</t>
+          <t>mental exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1199,28 +1166,33 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the time, effort, financial cost, or aversiveness of enacting a behaviour.</t>
+          <t>A behavioural attribute that is the level of mental effort expended on the behaviour to be enacted.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>The mental effort required to perform a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050814</t>
+          <t>BCIO:050464</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>emotionally driven</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>high mental exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1228,28 +1200,33 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A behavioural attribute in which the behaviour is caused by an emotion process.</t>
+          <t>Mental exertion expended on a behaviour that is high.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>High mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:036076</t>
+          <t>BCIO:050468</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>impulsiveness</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>low mental exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1257,7 +1234,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is to what extent the behaviour is a direct emotional, habitual or instinctive reaction to something.</t>
+          <t>Mental exertion expended on a behaviour that is low.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1265,30 +1242,25 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>How far a behaviour is enacted without thinking.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>This class is a dimension and can be construed as the obverse of reflectiveness and so operationalised in terms of acting without thinking.</t>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Low mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050902</t>
+          <t>BCIO:050433</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>behavioural ease</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>cognitive exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1296,36 +1268,41 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the level of convenience, ease or comfort of a behaviour.</t>
+          <t>Mental exertion expended on a behaviour where the exertion involves cognitive processes.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>The effort relating to thinking required to perform a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050447</t>
+          <t>BCIO:050462</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>intentionality</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>high cognitive exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A behavioural attribute that is the extent to which the behaviour is caused by a behavioural intention.</t>
+          <t>Cognitive exertion expended on a behaviour that is high.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1333,67 +1310,67 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>How far a behaviour is enacted as a direct result of a conscious intention to enact it.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>This class is a dimension and is differentiated from reflectiveness because a behaviour may be fully intentional but involve little reflective thought, e.g., when driving carelessly. In this class the intention relates to the behaviour itself. If a person intends to do one thing but accidentally does something else it does not count as intentional in this class, e.g., if someone intends to injure someone else and ends up killing them, that would not count as intentionally killing them.</t>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>High cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050839</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>task complexity</t>
-        </is>
-      </c>
+          <t>BCIO:050470</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>moderate cognitive exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A process attribute that is the complexity of thought or behaviour required to achieve a goal.</t>
+          <t>Cognitive exertion expended on a behaviour that is medium.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Moderate cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
+          <t>BCIO:050466</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>low cognitive exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+          <t>Cognitive exertion expended on a behaviour that is low.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1401,29 +1378,25 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Striated muscles referred to in the definition do not ordinarily involve cardiac muscles.
-Behaviours are usually in response to an internal or external stimuli.
-Every behaviour is associated with mental processes, but not every mental process is associated with behaviour. For instance, a verbal communication behaviour will involve mental processes to produce speech. However, mental processes associated with listening can occur without a person performing a behaviour.
-'behaviours' can involve a series of activities (e.g., more granular behaviours).
-'A 'striated muscle' can defined as 'a type of contractile tissue that is marked by transverse striations; it is concerned with moving skeletal parts to which it is usually attached.' (https://www.collinsdictionary.com/dictionary/english/striped-muscle)</t>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Low cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050440</t>
+          <t>BCIO:050472</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>position-related behaviour</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>moderate mental exertion expended on a behaviour</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1431,26 +1404,31 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the enactor's posture or location.</t>
+          <t>Mental exertion expended on a behaviour that is medium.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Moderate mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:036029</t>
+          <t>BCIO:050434</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>posture behaviour</t>
+          <t>emotional management exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1460,19 +1438,24 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A position-related behaviour that involves adopting a body configuration in relation to the immediate environment.</t>
+          <t>Mental exertion expended on a behaviour where the exertion involves control over emotions or their expression.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>The effort a person has to exert to manage their emotions when performing a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050460</t>
+          <t>BCIO:050467</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1480,7 +1463,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>postural expressive behaviour</t>
+          <t>low emotional management exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1489,7 +1472,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A posture behaviour that is expressive.</t>
+          <t>Emotional management exertion expended on a behaviour that is low.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1497,16 +1480,16 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>If postural behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using body language’ (BCIO:050424)</t>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Low emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:036068</t>
+          <t>BCIO:050463</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1514,7 +1497,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>reclining</t>
+          <t>high emotional management exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1523,19 +1506,24 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A posture behaviour in which one's weight is supported by one's buttocks and back rather than one's feet, and in which one's back rests on a surface at an angle that is greater than 90 degrees and less than 180 degrees.</t>
+          <t>Emotional management exertion expended on a behaviour that is high.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>High emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:036069</t>
+          <t>BCIO:050471</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1543,7 +1531,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>sitting</t>
+          <t>moderate emotional management exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1552,65 +1540,80 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A posture behaviour in which one's weight is supported by one's buttocks rather than one's feet, and in which one's back is upright.</t>
+          <t>Emotional management exertion expended on a behaviour that is medium.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Moderate emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:036067</t>
+          <t>BCIO:050447</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>intentionality</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>lying down</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A posture behaviour that involves being in a horizontal position on a supporting surface</t>
+          <t>A behavioural attribute that is the extent to which the behaviour is caused by a behavioural intention.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>How far a behaviour is enacted as a direct result of a conscious intention to enact it.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>This class is a dimension and is differentiated from reflectiveness because a behaviour may be fully intentional but involve little reflective thought, e.g., when driving carelessly. In this class the intention relates to the behaviour itself. If a person intends to do one thing but accidentally does something else it does not count as intentional in this class, e.g., if someone intends to injure someone else and ends up killing them, that would not count as intentionally killing them.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:036070</t>
+          <t>BCIO:050822</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>identity congruence</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>standing</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A posture behaviour in which one has or is maintaining an upright position while supported by one's feet</t>
+          <t>A behavioural attribute that is the extent to which one’s behaviour is believed to be consistent with one’s core, positive self-identity.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1622,16 +1625,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:036026</t>
+          <t>BCIO:050814</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>locomotive behaviour</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>emotionally driven</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1639,7 +1642,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A position-related behaviour in which muscles are used by a person to move themselves relative to the immediate environment or part of it.</t>
+          <t>A behavioural attribute in which the behaviour is caused by an emotion process.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1651,43 +1654,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:036108</t>
+          <t>BCIO:050444</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>behavioural reflectiveness</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>walking</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A locomotive behaviour that involves moving at a regular pace by lifting and setting down each foot in turn, never having both feet off the ground at once.</t>
+          <t>A behavioural attribute that is the degree to which the behaviour is under the control of reflective motivation.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>How far a behaviour is enacted after thinking about it and its consequences.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>This class is a dimension and involves any conscious thought processes that lead to a behaviour in some way, even if those processes are themselves influenced by emotional processes and biases.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:036059</t>
+          <t>BCIO:050833</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>travel behaviour</t>
+          <t>reflectively controlled</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1697,60 +1710,64 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A position-related behaviour that involves changing physical location.</t>
+          <t>Behavioural reflectiveness in which the behaviour is predominantly controlled by reflective motivation.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Travel refers to some form of relocation from a place or position to another.
-The classes 'travel behaviour' and 'locomotive behaviour' have many instances in which they overlap. However, there are also examples where these classes are not the same. For instance, running on a treadmill is a locomotive behaviour but not a travel behaviour.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:036064</t>
+          <t>BCIO:036076</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>impulsiveness</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>transporting behaviour</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A travel behaviour that involves moving an object in addition toother than the actor.</t>
+          <t>A behavioural attribute that is to what extent the behaviour is a direct emotional, habitual or instinctive reaction to something.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>How far a behaviour is enacted without thinking.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>This class is a dimension and can be construed as the obverse of reflectiveness and so operationalised in terms of acting without thinking.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050443</t>
+          <t>BCIO:050432</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>experience-related behaviour</t>
+          <t>physical exertion expended on a behaviour</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1761,26 +1778,31 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>An &lt;individual human behaviour&gt; that relates to something the person experiences.</t>
+          <t>A behavioural attribute that is the level of musculoskeletal work expended on the behaviour to be enacted.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>The physical effort required to perform a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050421</t>
+          <t>BCIO:050473</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>distress minimisation behaviour</t>
+          <t>moderate physical exertion expended on behaviour</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1790,7 +1812,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves avoiding, reducing or escaping anxiety, stress, sorrow, shame and unhappiness.</t>
+          <t>Physical exertion expended on a behaviour that is medium.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -1800,21 +1822,21 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>distress minimization behaviour</t>
+          <t>Moderate physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050834</t>
+          <t>BCIO:050465</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>regulatory behaviour</t>
+          <t>high physical exertion expended on behaviour</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1824,7 +1846,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves monitoring and acting upon some parts of the person or their environment.</t>
+          <t>Physical exertion expended on a behaviour that is high</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -1832,54 +1854,59 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Environment here includes the social and physical environment and includes behaviours involved in monitoring of others or self, action planning, and goal setting.</t>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>High physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050811</t>
+          <t>BCIO:050469</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>cue management behaviour</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>low physical exertion expended on behaviour</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>A regulatory behaviour in which cues that prompt a behaviour pattern are added, altered or removed.</t>
+          <t>Physical exertion expended on a behaviour that is low.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050841</t>
+          <t>BCIO:050430</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>approach behaviour</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>behavioural form</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1887,28 +1914,33 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves taking action to engage with some stimulus that is judged to be rewarding by the person.</t>
+          <t>A behavioural attribute that is the physical way in which a behaviour is enacted.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The way in which the behaviour is performed, including the shape of one’s muscles and skeletal alignment during the behaviour. </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:036112</t>
+          <t>BCIO:050902</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>spiritual behaviour</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>behavioural ease</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1916,7 +1948,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that is performed in line with a belief system that is grounded in reverence for a supernatural power or powers and provides meaning in life.</t>
+          <t>A behavioural attribute that is the level of convenience, ease or comfort of a behaviour.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -1928,16 +1960,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:036008</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>BCIO:050839</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>task complexity</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>learning behaviour</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1945,7 +1977,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves improving knowledge or skill.</t>
+          <t>A process attribute that is the complexity of thought or behaviour required to achieve a goal.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -1957,24 +1989,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:050291</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>BCIO:036000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>individual human behaviour</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>knowledge development behaviour</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A learning behaviour that involves improving a person's knowledge.</t>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -1984,65 +2016,64 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>information acquisition behaviour; knowledge seeking behaviour</t>
+          <t>Striated muscles referred to in the definition do not ordinarily involve cardiac muscles.
+Behaviours are usually in response to an internal or external stimuli.
+Every behaviour is associated with mental processes, but not every mental process is associated with behaviour. For instance, a verbal communication behaviour will involve mental processes to produce speech. However, mental processes associated with listening can occur without a person performing a behaviour.
+'behaviours' can involve a series of activities (e.g., more granular behaviours).
+'A 'striated muscle' can defined as 'a type of contractile tissue that is marked by transverse striations; it is concerned with moving skeletal parts to which it is usually attached.' (https://www.collinsdictionary.com/dictionary/english/striped-muscle)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050825</t>
+          <t>BCIO:050812</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>domestic behaviour</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>monitoring behaviour</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A knowledge development behaviour that involves gathering information over a period of time.</t>
+          <t>An individual human behaviour within a residential facility.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>This is often used in relation to regulatory behaviour, either oneself or others. 'Monitoring behaviour' has part 'regulatory behaviour'</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050807</t>
+          <t>BCIO:050846</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>behavioural substitution</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>carer monitoring of child behaviour</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A monitoring behaviour in which a carer gathers information about the activities of some child in their care.</t>
+          <t>An &lt;individual human behaviour&gt; in which a person substitutes a more desired behaviour for a less desired behaviour.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2054,24 +2085,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:050824</t>
+          <t>BCIO:050819</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>harm preventing behaviour</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>knowledge acquisition about reducing harmful behaviours</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A knowledge development behaviour where the knowledge is about how to reduce or avoid a harmful behaviour.</t>
+          <t>An individual human behaviour that has an outcome to prevent harm.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2083,24 +2114,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:036039</t>
+          <t>BCIO:050818</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal-directed behaviour</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>skill development behaviour</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A learning behaviour that involves improving the ability to perform physical, psychological or social activities.</t>
+          <t>An individual human behaviour that has a behavioural goal.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2112,14 +2143,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:036073</t>
+          <t>BCIO:050920</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avoidance behaviour</t>
+          <t>opportunity-seeking behaviour</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2129,26 +2160,21 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves taking defensive action in order to avoid some stimulus judged to be aversive by the person.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>behaviour</t>
+          <t>A goal-directed behaviour whose goal is to search for and find opportunities that help meet needs or support attaining goals.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:050813</t>
+          <t>BCIO:050840</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>emotional behaviour</t>
+          <t>threat-reducing behaviour</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2158,26 +2184,31 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that is caused by an emotion process.</t>
+          <t>A goal-directed behaviour that has a goal to reduce threat.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Reducing a threat involves trying to reduce the harm of something that may occur in the future.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:036041</t>
+          <t>BCIO:050802</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>mind-body behaviour</t>
+          <t>approval seeking behaviour</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2187,7 +2218,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that aims to create a sense of interconnectedness between the mind and the body.</t>
+          <t>A goal-directed behaviour whose goal is to obtain the approval of another person.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2199,16 +2230,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:036030</t>
+          <t>BCIO:050439</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>sexual behaviour</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>material entity-related behaviour</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -2216,31 +2247,26 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that involves sexual arousal.</t>
+          <t>An individual human behaviour that relates to a material entity.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>The classes 'reproductive behaviour' and 'sexual behaviour' have some instances in which they would overlap. For instance, a subclass of both of these classes would be 'reproductive sexual behaviour'. Examples for 'reproductive sexual behaviour' can be annotated by using the two classes: 'reproductive behaviour' and 'sexual behaviour'. There are also various examples in which the classes 'reproductive behaviour' does not overlap with sexual behaviour. For instance, fertility preservation would be a reproductive behaviour but not a sexual behaviour. Similarly, various sexual behaviours do not have a reproductive function. For instance, performing oral sex may not have a reproductive function.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:036047</t>
+          <t>BCIO:050426</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>enjoyment behaviour</t>
+          <t>physical contact behaviour</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2250,7 +2276,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>An experience-related behaviour that is performed to experience pleasure or satisfaction.</t>
+          <t>A material-entity related behaviour that makes physical contact with something.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -2262,24 +2288,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050812</t>
+          <t>BCIO:036028</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>domestic behaviour</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>physical impact behaviour</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>An individual human behaviour within a residential facility.</t>
+          <t>A physical contact behaviour that is forceful.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -2291,16 +2317,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:050846</t>
+          <t>BCIO:036027</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>behavioural substitution</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>object-using behaviour</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -2308,36 +2334,41 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>An &lt;individual human behaviour&gt; in which a person substitutes a more desired behaviour for a less desired behaviour.</t>
+          <t>A material-entity related behaviour that uses a non-living object.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Non-living objects can include engineered artifacts, grain of sand and/or molecules.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:036062</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>socially-related behaviour</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>manufacturing behaviour</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
+          <t>An object-using behaviour that involves making a product from raw materials or parts.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -2349,42 +2380,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:036086</t>
+          <t>BCIO:050418</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>nurture behaviour</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>watching behaviour</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that involves meeting the physical, psychological or social needs of another living being to promote its development.</t>
+          <t>An object-using behaviour that involves deriving meaning from visual or audiovisual material.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>The term 'animal' in the definition includes humans and other animals.
-There can be different dimensions of nurturing, e.g., in some cases, nurturing can involve addressing someone's physical needs (e.g., feeding) but not emotional needs.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:050826</t>
+          <t>BCIO:050420</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2392,7 +2417,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>parenting behaviour</t>
+          <t>digital interaction behaviour</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2401,7 +2426,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Nurture behaviour that is provided to a young person by someone in a parent role.</t>
+          <t>An object-using behaviour that involves interacting with programs, procedures, documentation or data on an electronic device.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -2413,24 +2438,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:036066</t>
+          <t>BCIO:036063</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>pro-social behaviour</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>reading behaviour</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that a population judges to accord with current norms of positive social conduct.</t>
+          <t>An object-using behaviour that involves deriving meaning from written or printed symbols.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -2442,24 +2467,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:036072</t>
+          <t>BCIO:050427</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>antisocial behaviour</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>audio presentation listening behaviour</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that a population judges to be is contrary to the laws or accepted current norms of social conduct within a specific social context and causes annoyance and or disapproval in others.</t>
+          <t>An object-using  behaviour that involves attending to audiomaterial.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -2471,53 +2496,63 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:050810</t>
+          <t>BCIO:036007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>criminal behaviour</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>environmental system management behaviour</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>An antisocial behaviour that is illegal in a jurisdiction.</t>
+          <t>A material-entity related behaviour that involves creating, maintaining, adapting or destroying aspects of the physical or social environment system.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Behaviour that involves changing the physical or social environment.</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Environmental system is defined as "A system which has the disposition to environ one or more material entities." (http://purl.obolibrary.org/obo/ENVO_01000254). Accordingly, an environmental system is the social and physical environment surrounding a person.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:050816</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>environmental sustainability behaviour</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+          <t>An environmental system management behaviour that contributes to sustaining the ecosystem.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -2529,7 +2564,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:036036</t>
+          <t>BCIO:036005</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2537,7 +2572,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>physical combat behaviour</t>
+          <t>object management behaviour</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2546,7 +2581,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>An inter-personal behaviour that involves taking part in a physical struggle involving contact or the use of weapons</t>
+          <t>An environmental system management behaviour that involves creating, maintaining, adapting or destroying non-sentient objects.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -2554,40 +2589,45 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Physical combat behaviour can be aggressive but does not need to be. For instance, people can fight as part of a game.</t>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Objects can include engineered artifacts, organisms, grain of sand and/or molecules. The phrase ‘non-sentient objects’ is used to refer to objects that do not have a central nervous system.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050672</t>
+          <t>BCIO:036061</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>group facilitation behaviour</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>consumption behaviour</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>An &lt;inter-personal behaviour&gt; of a member of a social group that promotes engagement of members of the group in group behaviours.</t>
+          <t>A material entity-related behaviour that involves ingesting material into the body.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>behaviour</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:050397</t>
+          <t>BCIO:050417</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2595,7 +2635,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>social support behaviour</t>
+          <t>oral consumption</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2604,7 +2644,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>An inter-personal behaviour that involves providing physical, psychological or social assistance to another.</t>
+          <t>A consumption behaviour that involves putting a material into one’s mouth and swallowing this material.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -2616,7 +2656,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:036033</t>
+          <t>BCIO:050422</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2625,7 +2665,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>care-giving behaviour</t>
+          <t>drinking</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2633,7 +2673,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>A social support behaviour that involves meeting another person’s physical, psychological or social needs that this person is unable to fully meet themselves at a given moment.</t>
+          <t>Oral consumption behaviour that involves swallowing a liquid material.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -2645,24 +2685,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:006099</t>
+          <t>BCIO:050423</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>social influence behaviour</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>eating</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>An &lt;inter-personal behaviour&gt; where a person exerts an influence on the behaviour of another.</t>
+          <t>Oral consumption behaviour that involves chewing and swallowing some solid components</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -2674,24 +2714,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:050836</t>
+          <t>BCIO:050396</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>rewarding behaviour</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>transdermal consumption</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A social influence behaviour in which the person provides a positive stimulus contingent on another person’s behaviour.</t>
+          <t>A consumption behaviour that involves applying a material to the skin and ingesting this material into the circulation through the skin.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -2703,24 +2743,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:036089</t>
+          <t>BCIO:050394</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>political behaviour</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>inhaling consumption</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that aims to bring about or oppose political or social change.</t>
+          <t>A consumption behaviour that involves breathing in a material through the nose or mouth.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -2732,95 +2772,99 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:006095</t>
+          <t>BCIO:050379</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>normative behaviour</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>vaping device use</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A &lt;socially-related behaviour&gt; that is commonly enacted by people that are part of a social environmental system.</t>
+          <t>Inhaling consumption that involves using a device to consume an aerosol.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>behaviour</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:036011</t>
+          <t>BCIO:050378</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>social organisation behaviour</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>electronic vaping device use</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that involves a person contributing to the functioning of a social structure or a person in relation to a social structure.</t>
+          <t>Inhaling consumption that involves the use of an electronic vaping device.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>In the definition, the term 'contributing' can refer 'joining or integrating into a group or improving or maintaining the functioning within a group'
-'social structure' can relate to a social network or group.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:036084</t>
+          <t>BCIO:050377</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>association behaviour</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>e-cigarette use</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>A social organisation behaviour that involves increasing a sense of being part of a social group or dyad.</t>
+          <t>Inhaling consumption that involves using an e-cigarette.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>E-cigarettes do not necessarily have to include nicotine but can involve inhaling flavourings or other chemicals.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:050803</t>
+          <t>BCIO:050395</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2829,7 +2873,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>association behaviour with a pro-social group</t>
+          <t>sniffing consumption</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -2837,7 +2881,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>An association behaviour that involves increasing a sense of being part of a pro-social group.</t>
+          <t>Inhaling consumption that involves breathing in a material through the nose.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -2849,24 +2893,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:036035</t>
+          <t>BCIO:036113</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>economic behaviour</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>substance use behaviour</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>A socially-related behaviour that involves the production, acquisition, distribution or exchange of money, goods or services.</t>
+          <t>A consumption behaviour that involves ingesting a psychoactive substance into the body.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -2876,32 +2920,36 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>behaviours, such as economic behaviour, can involve a series of activities (e.g., more granular behaviours).
-The term 'production' in the definition specifically refers to the 'production of goods and services for value exchange'</t>
+          <t>substance use</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Substance use behaviour is not equated with substance abuse.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:050829</t>
+          <t>BCIO:050376</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>purchasing behaviour</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>alcohol consumption</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>An economic behaviour in which the person gives money in exchange for a service or ownership of a product.</t>
+          <t>A substance use behaviour that involves drinking an alcohol-containing product.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -2913,53 +2961,58 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:050837</t>
+          <t>BCIO:036114</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>selling behaviour</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>tobacco use behaviour</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>An economic behaviour in which the person provides a service or ownership of a product in exchange for money.</t>
+          <t>A substance use behaviour that involves ingesting constituents of a tobacco-containing product.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>tobacco use</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:036110</t>
+          <t>BCIO:036103</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>employment behaviour</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>tobacco smoking behaviour</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>An economic behaviour that involves a paid work agreement between an employer and an employee.</t>
+          <t>A tobacco use behaviour that involves setting light to a combustible tobacco product and ingesting the tobacco smoke that is produced.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -2969,31 +3022,31 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>behaviours', such as employment behaviour, can involve a series of activities (e.g., more granular behaviours).</t>
+          <t>smoking</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:050809</t>
+          <t>BCIO:036105</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>coping behaviour</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>cigarette smoking behaviour</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>An individual human behaviour that has the goal to reduce harm or discomfort.</t>
+          <t>A tobacco smoking behaviour that involves setting light to one end of a cigarette, putting the other end to the lips and sucking in order to ingest cigarette smoke.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -3005,82 +3058,97 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:050439</t>
+          <t>BCIO:050412</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>material entity-related behaviour</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>medication-taking</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to a material entity.</t>
+          <t>A consumption behaviour that involves ingesting a medicine to treat or relieve symptoms of a health condition or maintain an aspect of health or wellbeing.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>pharmacological consumption</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Medicine is defined as type of drug, i.e., ‘any substance which when absorbed into a living organism may modify one or more of its functions.’ (http://purl.obolibrary.org/obo/CHEBI_23888)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:050426</t>
+          <t>BCIO:050415</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>physical contact behaviour</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>self-injecting consumption</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A material-entity related behaviour that makes physical contact with something.</t>
+          <t>A consumption behaviour that involves administering a liquid into one’s body with a needle and a syringe.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>In the definition, ‘a needle and a springe’ include both a standard needle and syringe but also an autoinjector.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:036028</t>
+          <t>BCIO:050393</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>physical impact behaviour</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>intravenous self-injecting</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>A physical contact behaviour that is forceful.</t>
+          <t>Self-injecting consumption that involves administering liquids into one’s veins.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -3092,16 +3160,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:036027</t>
+          <t>BCIO:036024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>object-using behaviour</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>personal bodily care behaviour</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -3109,7 +3177,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A material-entity related behaviour that uses a non-living object.</t>
+          <t>An individual human behaviour that attends to one’s own hygiene, comfort or appearance.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -3117,33 +3185,33 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Non-living objects can include engineered artifacts, grain of sand and/or molecules.</t>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Behaviour relating to supporting the personal care of others can be captured under the class 'social support behaviour'.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:050427</t>
+          <t>BCIO:050368</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>audio presentation listening behaviour</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>bodily hygiene behaviour</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>An object-using  behaviour that involves attending to audiomaterial.</t>
+          <t>A personal bodily care behaviour that attends to hygiene by cleaning or washing oneself or parts of the body.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -3155,7 +3223,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:036063</t>
+          <t>BCIO:050369</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3163,7 +3231,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>reading behaviour</t>
+          <t>handwashing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -3172,7 +3240,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>An object-using behaviour that involves deriving meaning from written or printed symbols.</t>
+          <t>A bodily hygiene behaviour that involves cleaning or washing one's hands.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -3184,7 +3252,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:050420</t>
+          <t>BCIO:050370</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3192,7 +3260,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>digital interaction behaviour</t>
+          <t>dental hygiene behaviour</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -3201,7 +3269,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>An object-using behaviour that involves interacting with programs, procedures, documentation or data on an electronic device.</t>
+          <t>A bodily hygiene behaviour that attends to oral heath by cleaning one's teeth, gums or tongue.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -3213,53 +3281,58 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:050418</t>
+          <t>BCIO:050411</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>watching behaviour</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>sun protective behaviour</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>An object-using behaviour that involves deriving meaning from visual or audiovisual material.</t>
+          <t>A personal bodily care behaviour that involves protecting one's skin or eyes from the damaging effects of the sun.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>‘Sun protective behaviour’ is defined in terms of its goal (to protect oneself from the damaging effects of the sun) and can include very different behaviours, e.g., applying sunscreen and staying in the shade.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:036062</t>
+          <t>BCIO:050372</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>manufacturing behaviour</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>appearance-based bodily behaviour</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>An object-using behaviour that involves making a product from raw materials or parts.</t>
+          <t>A personal bodily care behaviour that attends to making changes to one's body to achieve a desired appearance.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -3271,14 +3344,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:036061</t>
+          <t>BCIO:050371</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>consumption behaviour</t>
+          <t>dressing behaviour</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3288,7 +3361,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A material entity-related behaviour that involves ingesting material into the body.</t>
+          <t>A personal bodily care behaviour that involves wearing clothes providing comfort and protecting oneself from ambient conditions.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -3300,92 +3373,87 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:036113</t>
+          <t>BCIO:036075</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>harmful behaviour</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>substance use behaviour</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves ingesting a psychoactive substance into the body.</t>
+          <t>An individual human behaviour that causes net harm.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Substance use behaviour is not equated with substance abuse.</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>substance use</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:050376</t>
+          <t>BCIO:036014</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>self-injury behaviour</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>alcohol consumption</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>A substance use behaviour that involves drinking an alcohol-containing product.</t>
+          <t>A harmful behaviour that involves intentionally causing oneself physical harm.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>There can be different reasons for engaging in self-injury behaviours, including to deal with difficult feelings and memories.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:036114</t>
+          <t>BCIO:050398</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>harmful behaviour to others</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>tobacco use behaviour</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A substance use behaviour that involves ingesting constituents of a tobacco-containing product.</t>
+          <t>A harmful behaviour that involves interacting with another animal  and thereby causing harm to its health, wellbeing or social functioning.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -3395,140 +3463,142 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>tobacco use</t>
+          <t>The term 'animal' in the definition includes humans and other animals.
+‘Harmful behaviour to others’ will involve a direct interaction between the person performing the behaviour and the person or animal that is negatively affected.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:036103</t>
+          <t>BCIO:036037</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>harassment behaviour</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>tobacco smoking behaviour</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>A tobacco use behaviour that involves setting light to a combustible tobacco product and ingesting the tobacco smoke that is produced.</t>
+          <t>Harmful behaviour to others that entails intentionally targeting someone with a behaviour that has the effect of causing distress in the targeted person.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>smoking</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:036105</t>
+          <t>BCIO:036032</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>bullying behaviour</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>cigarette smoking behaviour</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>A tobacco smoking behaviour that involves setting light to one end of a cigarette, putting the other end to the lips and sucking in order to ingest cigarette smoke.</t>
+          <t>A harassment behaviour that involves targeting someone through deliberate misuse of power in a relationship to inflict physical, social or psychological harm.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>While bullying behaviours can be directed at anyone, they are often aimed at certain people because of their race, religion, gender or sexual orientation or any other aspect such as appearance or disability (https://www.ncab.org.au/bullying-advice/bullying-for-parents/definition-of-bullying/).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:050415</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>socially-related behaviour</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>self-injecting consumption</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves administering a liquid into one’s body with a needle and a syringe.</t>
+          <t>An individual human behaviour that relates to the social environment.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>In the definition, ‘a needle and a springe’ include both a standard needle and syringe but also an autoinjector.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:050393</t>
+          <t>BCIO:036035</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>economic behaviour</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>intravenous self-injecting</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Self-injecting consumption that involves administering liquids into one’s veins.</t>
+          <t>A socially-related behaviour that involves the production, acquisition, distribution or exchange of money, goods or services.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>behaviours, such as economic behaviour, can involve a series of activities (e.g., more granular behaviours).
+The term 'production' in the definition specifically refers to the 'production of goods and services for value exchange'</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:050412</t>
+          <t>BCIO:050829</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3536,7 +3606,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>medication-taking</t>
+          <t>purchasing behaviour</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -3545,29 +3615,19 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves ingesting a medicine to treat or relieve symptoms of a health condition or maintain an aspect of health or wellbeing.</t>
+          <t>An economic behaviour in which the person gives money in exchange for a service or ownership of a product.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Medicine is defined as type of drug, i.e., ‘any substance which when absorbed into a living organism may modify one or more of its functions.’ (http://purl.obolibrary.org/obo/CHEBI_23888)</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>pharmacological consumption</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:050394</t>
+          <t>BCIO:050837</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3575,7 +3635,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>inhaling consumption</t>
+          <t>selling behaviour</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -3584,7 +3644,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves breathing in a material through the nose or mouth.</t>
+          <t>An economic behaviour in which the person provides a service or ownership of a product in exchange for money.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -3596,128 +3656,140 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:050379</t>
+          <t>BCIO:036110</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>vaping device use</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>employment behaviour</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Inhaling consumption that involves using a device to consume an aerosol.</t>
+          <t>An economic behaviour that involves a paid work agreement between an employer and an employee.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>behaviours', such as employment behaviour, can involve a series of activities (e.g., more granular behaviours).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:050378</t>
+          <t>BCIO:036086</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>nurture behaviour</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>electronic vaping device use</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Inhaling consumption that involves the use of an electronic vaping device.</t>
+          <t>A socially-related behaviour that involves meeting the physical, psychological or social needs of another living being to promote its development.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>The term 'animal' in the definition includes humans and other animals.
+There can be different dimensions of nurturing, e.g., in some cases, nurturing can involve addressing someone's physical needs (e.g., feeding) but not emotional needs.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:050377</t>
+          <t>BCIO:050826</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>parenting behaviour</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>e-cigarette use</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Inhaling consumption that involves using an e-cigarette.</t>
+          <t>Nurture behaviour that is provided to a young person by someone in a parent role.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>E-cigarettes do not necessarily have to include nicotine but can involve inhaling flavourings or other chemicals.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:050395</t>
+          <t>BCIO:036011</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>social organisation behaviour</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>sniffing consumption</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Inhaling consumption that involves breathing in a material through the nose.</t>
+          <t>A socially-related behaviour that involves a person contributing to the functioning of a social structure or a person in relation to a social structure.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>In the definition, the term 'contributing' can refer 'joining or integrating into a group or improving or maintaining the functioning within a group'
+'social structure' can relate to a social network or group.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:050396</t>
+          <t>BCIO:036084</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -3725,7 +3797,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>transdermal consumption</t>
+          <t>association behaviour</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -3734,7 +3806,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves applying a material to the skin and ingesting this material into the circulation through the skin.</t>
+          <t>A social organisation behaviour that involves increasing a sense of being part of a social group or dyad.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -3746,24 +3818,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:050417</t>
+          <t>BCIO:050803</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>oral consumption</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>association behaviour with a pro-social group</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>A consumption behaviour that involves putting a material into one’s mouth and swallowing this material.</t>
+          <t>An association behaviour that involves increasing a sense of being part of a pro-social group.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -3775,53 +3847,48 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:050422</t>
+          <t>BCIO:006095</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>normative behaviour</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>drinking</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Oral consumption behaviour that involves swallowing a liquid material.</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>behaviour</t>
+          <t>A &lt;socially-related behaviour&gt; that is commonly enacted by people that are part of a social environmental system.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:050423</t>
+          <t>BCIO:036089</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>political behaviour</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>eating</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Oral consumption behaviour that involves chewing and swallowing some solid components</t>
+          <t>A socially-related behaviour that aims to bring about or oppose political or social change.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -3833,14 +3900,14 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:036007</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>environmental system management behaviour</t>
+          <t>inter-personal behaviour</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3850,29 +3917,19 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>A material-entity related behaviour that involves creating, maintaining, adapting or destroying aspects of the physical or social environment system.</t>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Behaviour that involves changing the physical or social environment.</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Environmental system is defined as "A system which has the disposition to environ one or more material entities." (http://purl.obolibrary.org/obo/ENVO_01000254). Accordingly, an environmental system is the social and physical environment surrounding a person.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:036005</t>
+          <t>BCIO:006099</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3880,7 +3937,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>object management behaviour</t>
+          <t>social influence behaviour</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -3889,41 +3946,36 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>An environmental system management behaviour that involves creating, maintaining, adapting or destroying non-sentient objects.</t>
+          <t>An &lt;inter-personal behaviour&gt; where a person exerts an influence on the behaviour of another.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Objects can include engineered artifacts, organisms, grain of sand and/or molecules. The phrase ‘non-sentient objects’ is used to refer to objects that do not have a central nervous system.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:050816</t>
+          <t>BCIO:050836</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>environmental sustainability behaviour</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>rewarding behaviour</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>An environmental system management behaviour that contributes to sustaining the ecosystem.</t>
+          <t>A social influence behaviour in which the person provides a positive stimulus contingent on another person’s behaviour.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -3935,24 +3987,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:050818</t>
+          <t>BCIO:050397</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>goal-directed behaviour</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>social support behaviour</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>An individual human behaviour that has a behavioural goal.</t>
+          <t>An inter-personal behaviour that involves providing physical, psychological or social assistance to another.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -3964,103 +4016,103 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:050920</t>
+          <t>BCIO:036033</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>opportunity-seeking behaviour</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>care-giving behaviour</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>A goal-directed behaviour whose goal is to search for and find opportunities that help meet needs or support attaining goals.</t>
+          <t>A social support behaviour that involves meeting another person’s physical, psychological or social needs that this person is unable to fully meet themselves at a given moment.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>behaviour</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:050802</t>
+          <t>BCIO:036036</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>approval seeking behaviour</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>physical combat behaviour</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>A goal-directed behaviour whose goal is to obtain the approval of another person.</t>
+          <t>An inter-personal behaviour that involves taking part in a physical struggle involving contact or the use of weapons</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Physical combat behaviour can be aggressive but does not need to be. For instance, people can fight as part of a game.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:050840</t>
+          <t>BCIO:050672</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>threat-reducing behaviour</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>group facilitation behaviour</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>A goal-directed behaviour that has a goal to reduce threat.</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Reducing a threat involves trying to reduce the harm of something that may occur in the future.</t>
+          <t>An &lt;inter-personal behaviour&gt; of a member of a social group that promotes engagement of members of the group in group behaviours.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:006158</t>
+          <t>BCIO:036072</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>habitual behaviour</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>antisocial behaviour</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -4068,31 +4120,36 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>An &lt;individual human behaviour&gt; that results from a learnt stimulus-behaviour co-occurrence.</t>
+          <t>A socially-related behaviour that a population judges to be is contrary to the laws or accepted current norms of social conduct within a specific social context and causes annoyance and or disapproval in others.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>behaviour</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:050810</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>expressive behaviour</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>criminal behaviour</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
+          <t>An antisocial behaviour that is illegal in a jurisdiction.</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -4104,14 +4161,14 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:036066</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>human communication behaviour</t>
+          <t>pro-social behaviour</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4121,7 +4178,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+          <t>A socially-related behaviour that a population judges to accord with current norms of positive social conduct.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -4133,24 +4190,24 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:050238</t>
+          <t>BCIO:050440</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>position-related behaviour</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which information is transmitted without being encoded in the meaning units of any language.</t>
+          <t>An individual human behaviour that relates to the enactor's posture or location.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -4162,87 +4219,88 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:050424</t>
+          <t>BCIO:036059</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>travel behaviour</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour using body language</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>A non-linguistic communication behaviour that involves expressing thoughts or feelings through bodily movement or posture.</t>
+          <t>A position-related behaviour that involves changing physical location.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Travel refers to some form of relocation from a place or position to another.
+The classes 'travel behaviour' and 'locomotive behaviour' have many instances in which they overlap. However, there are also examples where these classes are not the same. For instance, running on a treadmill is a locomotive behaviour but not a travel behaviour.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:036002</t>
+          <t>BCIO:036064</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>transporting behaviour</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour using gesture</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>A non-linguistic communication behaviour using body language involving a deliberately chosen movement of the head, neck, torso, or limbs to express an idea or feeling.</t>
+          <t>A travel behaviour that involves moving an object in addition toother than the actor.</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>Gestures are deliberately chosen by the person to communicate some message.  The meaning of a gesture may differ across different cultures.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:050425</t>
+          <t>BCIO:036026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>locomotive behaviour</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour using facial expression</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Non-linguistic communication behaviour using body language that involves movements of facial muscles to express thoughts or feelings.</t>
+          <t>A position-related behaviour in which muscles are used by a person to move themselves relative to the immediate environment or part of it.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -4254,24 +4312,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:050375</t>
+          <t>BCIO:036108</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>walking</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour using eye contact</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>A non-linguistic communication behaviour using body language characterised by the meeting of eyes with another individual.</t>
+          <t>A locomotive behaviour that involves moving at a regular pace by lifting and setting down each foot in turn, never having both feet off the ground at once.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -4283,24 +4341,24 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:050373</t>
+          <t>BCIO:036029</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>posture behaviour</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>non-linguistic communication behaviour using vocalisations</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>A non-linguistic communication behaviour using one's voice to produce sounds.</t>
+          <t>A position-related behaviour that involves adopting a body configuration in relation to the immediate environment.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -4312,7 +4370,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:036069</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4320,7 +4378,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>linguistic communication behaviour</t>
+          <t>sitting</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4329,7 +4387,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+          <t>A posture behaviour in which one's weight is supported by one's buttocks rather than one's feet, and in which one's back is upright.</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -4341,24 +4399,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:050458</t>
+          <t>BCIO:050460</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>facial expression behaviour</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>postural expressive behaviour</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the muscles of the face.</t>
+          <t>A posture behaviour that is expressive.</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -4366,72 +4424,62 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/MFOEM_000125</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>If facial expression behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using facial expression’ (BCIO:050425).</t>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>If postural behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using body language’ (BCIO:050424)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:050459</t>
+          <t>BCIO:036068</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>gesticulatory expressive behaviour</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>reclining</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>An expressive behaviour involving a movement of the limbs, head or torso.</t>
+          <t>A posture behaviour in which one's weight is supported by one's buttocks and back rather than one's feet, and in which one's back rests on a surface at an angle that is greater than 90 degrees and less than 180 degrees.</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>If the gesticulatory behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using gesture’ (BCIO:036002).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:036067</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>lying down</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+          <t>A posture behaviour that involves being in a horizontal position on a supporting surface</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -4443,24 +4491,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:050442</t>
+          <t>BCIO:036070</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>vocalisation behaviour</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>standing</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>An expressive behaviour involving vibration of the vocal chords.</t>
+          <t>A posture behaviour in which one has or is maintaining an upright position while supported by one's feet</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -4472,50 +4520,45 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:050461</t>
+          <t>BCIO:050832</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>reflective behaviour</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>talking</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>A vocalisation behaviour that expresses something using words.</t>
+          <t>An individual human behaviour that is caused by a reflective mental process.</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>If talking is enacted when communicating with someone, please refer to the class labelled ‘linguistic communication behaviour’ (BCIO:050237)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:050456</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>crying</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>expressive behaviour</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -4523,31 +4566,26 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves tears, and facial expressions of distress.</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/GO_0060273</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:050815</t>
+          <t>BCIO:036021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>emotionally expressive behaviour</t>
+          <t>creative expressive behaviour</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4557,26 +4595,31 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>An expressive behaviour that conveys some emotion.</t>
+          <t>An expressive behaviour that involves consciously using some capability to create or shape an aspect of the environment to express an idea or emotion.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>An aspect of the environment includes both objects within it but also processes (e.g., music performance or dancing).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:036021</t>
+          <t>BCIO:050442</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>creative expressive behaviour</t>
+          <t>vocalisation behaviour</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4586,60 +4629,60 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves consciously using some capability to create or shape an aspect of the environment to express an idea or emotion.</t>
+          <t>An expressive behaviour involving vibration of the vocal chords.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>An aspect of the environment includes both objects within it but also processes (e.g., music performance or dancing).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:050437</t>
+          <t>BCIO:050461</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>health-related behaviour</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>talking</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to health of oneself or others.</t>
+          <t>A vocalisation behaviour that expresses something using words.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>If talking is enacted when communicating with someone, please refer to the class labelled ‘linguistic communication behaviour’ (BCIO:050237)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:050821</t>
+          <t>BCIO:050815</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>health-promoting behaviour</t>
+          <t>emotionally expressive behaviour</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4649,31 +4692,26 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>A health-related behaviour that improves the person’s health.</t>
+          <t>An expressive behaviour that conveys some emotion.</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>This class is for behaviour that promote positive health as well as protect against threats to health.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:050413</t>
+          <t>BCIO:050458</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>providing healthcare</t>
+          <t>facial expression behaviour</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4683,36 +4721,46 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>A health-related behaviour that involves assessing, monitoring, improving or maintaining an aspect of another person’s health.</t>
+          <t>An expressive behaviour that involves the muscles of the face.</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/MFOEM_000125</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>If facial expression behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using facial expression’ (BCIO:050425).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:050359</t>
+          <t>BCIO:050459</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>administering vaccine</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>gesticulatory expressive behaviour</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves administering a vaccination to prevent or lower the risk of a disease.</t>
+          <t>An expressive behaviour involving a movement of the limbs, head or torso.</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -4720,33 +4768,33 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>Vaccination is defined as “a medical intervention that involves adding a vaccine into a host (e.g., human, mouse) in vivo with the intent to invoke an adaptive immune response.” (http://purl.obolibrary.org/obo/VO_0000002)</t>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>If the gesticulatory behaviour is enacted when communicating with someone, please refer to the class labelled ‘non-linguistic communication behaviour using gesture’ (BCIO:036002).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:050362</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>providing healthcare treatment</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves interacting with a person to improve or maintain aspects of this person’s health or wellbeing.</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -4758,24 +4806,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:050364</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>providing psychological treatment</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Providing healthcare treatment that uses communication or recommended tasks to assess and improve a person’s adaptive mental or behavioural functioning.</t>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -4787,24 +4835,24 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:050365</t>
+          <t>BCIO:050238</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>non-linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>providing creative arts therapy</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Providing psychological treatment that involves creative and expressive processes.</t>
+          <t>A human communication behaviour in which information is transmitted without being encoded in the meaning units of any language.</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -4816,7 +4864,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:050366</t>
+          <t>BCIO:050373</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -4825,7 +4873,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>providing occupational therapy</t>
+          <t>non-linguistic communication behaviour using vocalisations</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -4833,7 +4881,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Providing healthcare treatment that aims to enable people to participate in the activities of everyday life.</t>
+          <t>A non-linguistic communication behaviour using one's voice to produce sounds.</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -4845,7 +4893,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:050367</t>
+          <t>BCIO:050424</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -4854,7 +4902,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>providing speech and language therapy</t>
+          <t>non-linguistic communication behaviour using body language</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -4862,7 +4910,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Providing healthcare treatment that aims to improve or restore communication, eating, drinking or swallowing.</t>
+          <t>A non-linguistic communication behaviour that involves expressing thoughts or feelings through bodily movement or posture.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -4874,24 +4922,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:050363</t>
+          <t>BCIO:050425</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>providing physical therapy</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>non-linguistic communication behaviour using facial expression</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Providing healthcare treatment that involves advising, encouraging or physically supporting, a person to perform movements that remediate this person’s bodily impairments or promote mobility, function or quality of life.</t>
+          <t>Non-linguistic communication behaviour using body language that involves movements of facial muscles to express thoughts or feelings.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -4903,151 +4951,150 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:050414</t>
+          <t>BCIO:050375</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>diagnostic healthcare behaviour</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>non-linguistic communication behaviour using eye contact</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves assessing symptoms and signs in order to detect the nature of a health condition.</t>
+          <t>A non-linguistic communication behaviour using body language characterised by the meeting of eyes with another individual.</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Symptoms are experienced or felt by the individual (e.g., pain or a rash), while signs are observed or detected by the healthcare professional (e.g., low blood sugar). There can be overlap between symptoms and signs, as some symptoms can be observed or detected by a healthcare professional.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:050361</t>
+          <t>BCIO:036002</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>making a referral to another health care service</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>non-linguistic communication behaviour using gesture</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves directing a person to another healthcare professional or organisation to assess, monitor, improve or maintain an aspect of this person’s health or wellbeing.</t>
+          <t>A non-linguistic communication behaviour using body language involving a deliberately chosen movement of the head, neck, torso, or limbs to express an idea or feeling.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Gestures are deliberately chosen by the person to communicate some message.  The meaning of a gesture may differ across different cultures.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:050354</t>
+          <t>BCIO:050456</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>prescribing behaviour</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>crying</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves advising and authorising the use of a treatment to improve or maintain another person's health or wellbeing.</t>
+          <t>An expressive behaviour that involves tears, and facial expressions of distress.</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/GO_0060273</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:050355</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>prescribing medication</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Prescribing behaviour that involves advising and authorising the use of a medicine.</t>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Medicine is defined as type of drug, i.e., ‘any substance which when absorbed into a living organism may modify one or more of its functions.’ (http://purl.obolibrary.org/obo/CHEBI_23888)
-Prescribing medication can include advising and authorising to stop using a medicine.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:050356</t>
+          <t>BCIO:050437</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>health-related behaviour</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>prescribing behavioural regime</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Prescribing behaviour that involves advising and authorising the performance of a behaviour or a series of behaviours.</t>
+          <t>An individual human behaviour that relates to health of oneself or others.</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -5059,65 +5106,75 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:050357</t>
+          <t>BCIO:050821</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>health-promoting behaviour</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>social prescribing</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Prescribing behaviour that involves advising and authorising the participation in services targeting social, economic or environmental factors that affect health or wellbeing.</t>
+          <t>A health-related behaviour that improves the person’s health.</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>This class is for behaviour that promote positive health as well as protect against threats to health.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:050360</t>
+          <t>BCIO:050399</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>providing healthcare advice</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>utilising healthcare</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves communicating guidance or recommendations to improve or maintain another person’s health or wellbeing.</t>
+          <t>A health-related behaviour that involves interacting with a healthcare provider in order to assess, monitor, improve or maintain an aspect of one's health.</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>A ‘healthcare provider’ can be a person or organisation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:050358</t>
+          <t>BCIO:050404</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5125,7 +5182,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>reviewing prescribed medication</t>
+          <t>participating in healthcare treatment</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -5134,7 +5191,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Providing healthcare that involves assessing a person's health or wellbeing after a period of taking a prescribed medication and assessing whether the medication continues to be appropriate.</t>
+          <t>Utilising healthcare that involves engaging with a treatment regimen to improve or maintain aspects of one's health or wellbeing.</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -5146,24 +5203,24 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:050352</t>
+          <t>BCIO:050408</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>providing healthcare testing</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>participating in occupational therapy</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Providing a healthcare that involves a procedure to assess another person’s health or wellbeing.</t>
+          <t>Participating in healthcare treatment that aims to enable people to participate in the activities of everyday life.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -5175,7 +5232,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:050353</t>
+          <t>BCIO:050405</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5184,7 +5241,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>providing health screening</t>
+          <t>participating in physical therapy</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5192,7 +5249,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Providing healthcare testing to detect the presence of a health condition in a person who is asymptomatic for that condition.</t>
+          <t>Participating in healthcare treatment that involves advice, encouragement, or physical support to perform movements that remediate one’s bodily impairments or promote mobility, function or quality of life.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -5204,58 +5261,53 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:050399</t>
+          <t>BCIO:050409</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>utilising healthcare</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>participating in speech and language therapy</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>A health-related behaviour that involves interacting with a healthcare provider in order to assess, monitor, improve or maintain an aspect of one's health.</t>
+          <t>Participating in healthcare treatment that aims to improve or restore communication, eating, drinking or swallowing.</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>A ‘healthcare provider’ can be a person or organisation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:050404</t>
+          <t>BCIO:050801</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>participating in healthcare treatment</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>adherence to healthcare treatment</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Utilising healthcare that involves engaging with a treatment regimen to improve or maintain aspects of one's health or wellbeing.</t>
+          <t>Participating in healthcare treatment in accordance with treatment instructions.</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -5267,7 +5319,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BCIO:050409</t>
+          <t>BCIO:050406</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5276,7 +5328,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>participating in speech and language therapy</t>
+          <t>participating in psychological treatment</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -5284,7 +5336,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Participating in healthcare treatment that aims to improve or restore communication, eating, drinking or swallowing.</t>
+          <t>Participating in healthcare treatment that uses communication or recommended tasks to assess and improve adaptive mental or behavioural functioning.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -5296,24 +5348,24 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:050405</t>
+          <t>BCIO:050407</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>participating in physical therapy</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>participating in creative arts therapy</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Participating in healthcare treatment that involves advice, encouragement, or physical support to perform movements that remediate one’s bodily impairments or promote mobility, function or quality of life.</t>
+          <t>Participating in psychological treatment that involves creative and expressive processes.</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -5325,24 +5377,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:050406</t>
+          <t>BCIO:050400</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>participating in psychological treatment</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>arranging a healthcare service appointment</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Participating in healthcare treatment that uses communication or recommended tasks to assess and improve adaptive mental or behavioural functioning.</t>
+          <t>Utilising healthcare that involves scheduling a time to interact with a person or organisation providing healthcare.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -5354,36 +5406,41 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:050407</t>
+          <t>BCIO:050401</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>participating in healthcare testing</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>participating in creative arts therapy</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Participating in psychological treatment that involves creative and expressive processes.</t>
+          <t>Utilising healthcare that involves participating in a healthcare procedure to assess or monitor an aspect of one’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Healthcare procedure is defined as ‘a healthcare intervention that refers to any series of pre-defined steps that should be followed to achieve a desired result.’ </t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:050408</t>
+          <t>BCIO:050402</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5392,7 +5449,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>participating in occupational therapy</t>
+          <t>participating in health screening</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -5400,7 +5457,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Participating in healthcare treatment that aims to enable people to participate in the activities of everyday life.</t>
+          <t>Participating in healthcare testing to detect the presence of a health condition while asymptomatic for that condition.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -5412,99 +5469,104 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:050801</t>
+          <t>BCIO:050403</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>adherence to healthcare treatment</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>undergoing vaccination</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Participating in healthcare treatment in accordance with treatment instructions.</t>
+          <t>Utilising healthcare that involves interacting with a healthcare provider to receive a vaccination to prevent or lower the risk of a disease.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Vaccination is defined as “a medical intervention that involves in adding vaccine into a host (e.g., human, mouse) in vivo with the intent to invoke an adaptive immune response.” (http://purl.obolibrary.org/obo/VO_0000002)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BCIO:050401</t>
+          <t>BCIO:050413</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>participating in healthcare testing</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>providing healthcare</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Utilising healthcare that involves participating in a healthcare procedure to assess or monitor an aspect of one’s health or wellbeing.</t>
+          <t>A health-related behaviour that involves assessing, monitoring, improving or maintaining an aspect of another person’s health.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Healthcare procedure is defined as ‘a healthcare intervention that refers to any series of pre-defined steps that should be followed to achieve a desired result.’ </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BCIO:050402</t>
+          <t>BCIO:050359</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>participating in health screening</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>administering vaccine</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Participating in healthcare testing to detect the presence of a health condition while asymptomatic for that condition.</t>
+          <t>Providing healthcare that involves administering a vaccination to prevent or lower the risk of a disease.</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Vaccination is defined as “a medical intervention that involves adding a vaccine into a host (e.g., human, mouse) in vivo with the intent to invoke an adaptive immune response.” (http://purl.obolibrary.org/obo/VO_0000002)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BCIO:050403</t>
+          <t>BCIO:050354</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5512,7 +5574,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>undergoing vaccination</t>
+          <t>prescribing behaviour</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5521,70 +5583,71 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Utilising healthcare that involves interacting with a healthcare provider to receive a vaccination to prevent or lower the risk of a disease.</t>
+          <t>Providing healthcare that involves advising and authorising the use of a treatment to improve or maintain another person's health or wellbeing.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>Vaccination is defined as “a medical intervention that involves in adding vaccine into a host (e.g., human, mouse) in vivo with the intent to invoke an adaptive immune response.” (http://purl.obolibrary.org/obo/VO_0000002)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BCIO:050400</t>
+          <t>BCIO:050355</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>arranging a healthcare service appointment</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>prescribing medication</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Utilising healthcare that involves scheduling a time to interact with a person or organisation providing healthcare.</t>
+          <t>Prescribing behaviour that involves advising and authorising the use of a medicine.</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Medicine is defined as type of drug, i.e., ‘any substance which when absorbed into a living organism may modify one or more of its functions.’ (http://purl.obolibrary.org/obo/CHEBI_23888)
+Prescribing medication can include advising and authorising to stop using a medicine.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BCIO:050410</t>
+          <t>BCIO:050356</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>self-monitoring an aspect of health</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>prescribing behavioural regime</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>A health-related behaviour that uses a method to monitor and record an indicator of one’s health or wellbeing.</t>
+          <t>Prescribing behaviour that involves advising and authorising the performance of a behaviour or a series of behaviours.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -5596,24 +5659,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BCIO:036042</t>
+          <t>BCIO:050357</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>physical performance behaviour</t>
-        </is>
-      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>social prescribing</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>A health-related behaviour that involves maintenance or improvement of flexibility, strength, balance or cardiovascular fitness.</t>
+          <t>Prescribing behaviour that involves advising and authorising the participation in services targeting social, economic or environmental factors that affect health or wellbeing.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -5625,24 +5688,24 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BCIO:050819</t>
+          <t>BCIO:050361</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>harm preventing behaviour</t>
-        </is>
-      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>making a referral to another health care service</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>An individual human behaviour that has an outcome to prevent harm.</t>
+          <t>Providing healthcare that involves directing a person to another healthcare professional or organisation to assess, monitor, improve or maintain an aspect of this person’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -5654,58 +5717,53 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BCIO:036024</t>
+          <t>BCIO:050352</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>personal bodily care behaviour</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>providing healthcare testing</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>An individual human behaviour that attends to one’s own hygiene, comfort or appearance.</t>
+          <t>Providing a healthcare that involves a procedure to assess another person’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>Behaviour relating to supporting the personal care of others can be captured under the class 'social support behaviour'.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BCIO:050371</t>
+          <t>BCIO:050353</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>dressing behaviour</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>providing health screening</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>A personal bodily care behaviour that involves wearing clothes providing comfort and protecting oneself from ambient conditions.</t>
+          <t>Providing healthcare testing to detect the presence of a health condition in a person who is asymptomatic for that condition.</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -5717,24 +5775,24 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BCIO:050368</t>
+          <t>BCIO:050360</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>bodily hygiene behaviour</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>providing healthcare advice</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>A personal bodily care behaviour that attends to hygiene by cleaning or washing oneself or parts of the body.</t>
+          <t>Providing healthcare that involves communicating guidance or recommendations to improve or maintain another person’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -5746,7 +5804,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BCIO:050369</t>
+          <t>BCIO:050362</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5754,7 +5812,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>handwashing</t>
+          <t>providing healthcare treatment</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -5763,7 +5821,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>A bodily hygiene behaviour that involves cleaning or washing one's hands.</t>
+          <t>Providing healthcare that involves interacting with a person to improve or maintain aspects of this person’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -5775,24 +5833,24 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BCIO:050370</t>
+          <t>BCIO:050363</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>dental hygiene behaviour</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>providing physical therapy</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>A bodily hygiene behaviour that attends to oral heath by cleaning one's teeth, gums or tongue.</t>
+          <t>Providing healthcare treatment that involves advising, encouraging or physically supporting, a person to perform movements that remediate this person’s bodily impairments or promote mobility, function or quality of life.</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -5804,58 +5862,53 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BCIO:050411</t>
+          <t>BCIO:050366</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>sun protective behaviour</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>providing occupational therapy</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>A personal bodily care behaviour that involves protecting one's skin or eyes from the damaging effects of the sun.</t>
+          <t>Providing healthcare treatment that aims to enable people to participate in the activities of everyday life.</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>‘Sun protective behaviour’ is defined in terms of its goal (to protect oneself from the damaging effects of the sun) and can include very different behaviours, e.g., applying sunscreen and staying in the shade.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BCIO:050372</t>
+          <t>BCIO:050367</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>appearance-based bodily behaviour</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>providing speech and language therapy</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>A personal bodily care behaviour that attends to making changes to one's body to achieve a desired appearance.</t>
+          <t>Providing healthcare treatment that aims to improve or restore communication, eating, drinking or swallowing.</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -5867,24 +5920,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BCIO:050438</t>
+          <t>BCIO:050364</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>life function-related behaviour</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>providing psychological treatment</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>An individual human behaviour related to vital bodily functions.</t>
+          <t>Providing healthcare treatment that uses communication or recommended tasks to assess and improve a person’s adaptive mental or behavioural functioning.</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -5896,87 +5949,87 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BCIO:036056</t>
+          <t>BCIO:050365</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>reproductive behaviour</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>providing creative arts therapy</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>A life function-related behaviour that involves producing offspring based on combining DNA of two or more people.</t>
+          <t>Providing psychological treatment that involves creative and expressive processes.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>The classes 'reproductive behaviour' and 'sexual behaviour' have some instances in which they would overlap. For instance, a subclass of both of these classes would be 'reproductive sexual behaviour'. Examples for 'reproductive sexual behaviour' can be annotated by using the two classes: 'reproductive behaviour' and 'sexual behaviour'. There are also various examples in which the classes 'reproductive behaviour' does not overlap with sexual behaviour. For instance, fertility preservation would be a reproductive behaviour but not a sexual behaviour. Similarly, various sexual behaviours do not have a reproductive function. For instance, performing oral sex may not have a reproductive function.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BCIO:036057</t>
+          <t>BCIO:050414</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>breathing behaviour</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>diagnostic healthcare behaviour</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>A life function-related behaviour involves providing an appropriate level of oxygenation to body tissues.</t>
+          <t>Providing healthcare that involves assessing symptoms and signs in order to detect the nature of a health condition.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Symptoms are experienced or felt by the individual (e.g., pain or a rash), while signs are observed or detected by the healthcare professional (e.g., low blood sugar). There can be overlap between symptoms and signs, as some symptoms can be observed or detected by a healthcare professional.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BCIO:036054</t>
+          <t>BCIO:050358</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>excretion behaviour</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>reviewing prescribed medication</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>A life function-related behaviour that involves eliminating excess or harmful chemicals produced by bodily functions.</t>
+          <t>Providing healthcare that involves assessing a person's health or wellbeing after a period of taking a prescribed medication and assessing whether the medication continues to be appropriate.</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -5988,16 +6041,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BCIO:050832</t>
+          <t>BCIO:050410</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>reflective behaviour</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>self-monitoring an aspect of health</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
@@ -6005,7 +6058,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>An individual human behaviour that is caused by a reflective mental process.</t>
+          <t>A health-related behaviour that uses a method to monitor and record an indicator of one’s health or wellbeing.</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -6017,16 +6070,16 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BCIO:036075</t>
+          <t>BCIO:036042</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>harmful behaviour</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>physical performance behaviour</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
@@ -6034,7 +6087,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>An individual human behaviour that causes net harm.</t>
+          <t>A health-related behaviour that involves maintenance or improvement of flexibility, strength, balance or cardiovascular fitness.</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -6046,16 +6099,16 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BCIO:036014</t>
+          <t>BCIO:050443</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>self-injury behaviour</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>experience-related behaviour</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
@@ -6063,31 +6116,26 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>A harmful behaviour that involves intentionally causing oneself physical harm.</t>
+          <t>An &lt;individual human behaviour&gt; that relates to something the person experiences.</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>There can be different reasons for engaging in self-injury behaviours, including to deal with difficult feelings and memories.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BCIO:050398</t>
+          <t>BCIO:036008</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>harmful behaviour to others</t>
+          <t>learning behaviour</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -6097,25 +6145,19 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>A harmful behaviour that involves interacting with another animal  and thereby causing harm to its health, wellbeing or social functioning.</t>
+          <t>An experience-related behaviour that involves improving knowledge or skill.</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>The term 'animal' in the definition includes humans and other animals.
-‘Harmful behaviour to others’ will involve a direct interaction between the person performing the behaviour and the person or animal that is negatively affected.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BCIO:036037</t>
+          <t>BCIO:050291</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -6123,7 +6165,7 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>harassment behaviour</t>
+          <t>knowledge development behaviour</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -6132,19 +6174,24 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Harmful behaviour to others that entails intentionally targeting someone with a behaviour that has the effect of causing distress in the targeted person.</t>
+          <t>A learning behaviour that involves improving a person's knowledge.</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>information acquisition behaviour; knowledge seeking behaviour</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BCIO:036032</t>
+          <t>BCIO:050825</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -6153,7 +6200,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>bullying behaviour</t>
+          <t>monitoring behaviour</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
@@ -6161,7 +6208,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>A harassment behaviour that involves targeting someone through deliberate misuse of power in a relationship to inflict physical, social or psychological harm.</t>
+          <t>A knowledge development behaviour that involves gathering information over a period of time.</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -6169,127 +6216,112 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>While bullying behaviours can be directed at anyone, they are often aimed at certain people because of their race, religion, gender or sexual orientation or any other aspect such as appearance or disability (https://www.ncab.org.au/bullying-advice/bullying-for-parents/definition-of-bullying/).</t>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>This is often used in relation to regulatory behaviour, either oneself or others. 'Monitoring behaviour' has part 'regulatory behaviour'</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BCIO:050455</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>behavioural duration</t>
-        </is>
-      </c>
+          <t>BCIO:050807</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>carer monitoring of child behaviour</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>A temporal interval within which an individual human behaviour occurs.</t>
+          <t>A monitoring behaviour in which a carer gathers information about the activities of some child in their care.</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>The time between the start and end of a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BCIO:050449</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>abstinence duration</t>
-        </is>
-      </c>
+          <t>BCIO:050824</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>knowledge acquisition about reducing harmful behaviours</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>A temporal interval during which a person is abstinent from a behaviour.</t>
+          <t>A knowledge development behaviour where the knowledge is about how to reduce or avoid a harmful behaviour.</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>The time a person is abstinent from a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BCIO:050416</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>behavioural disposition</t>
-        </is>
-      </c>
+          <t>BCIO:036039</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>skill development behaviour</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>A bodily disposition that is realised as some behaviour.</t>
+          <t>A learning behaviour that involves improving the ability to perform physical, psychological or social activities.</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>A tendency to behave in a particular way.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BFO:0000034</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
+          <t>BCIO:050813</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>emotional behaviour</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
@@ -6297,7 +6329,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>A disposition that exists in virtue of the bearer’s physical make-up and this physical make-up is something the bearer possesses because it came into being, either through evolution (in the case of natural biological entities) or through intentional design (in the case of artifacts), in order to realize processes of a certain sort. (axiom label in BFO2 Reference: [064-001])</t>
+          <t>An experience-related behaviour that is caused by an emotion process.</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -6309,16 +6341,16 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BCIO:036001</t>
+          <t>BCIO:050421</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>human life function</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>distress minimisation behaviour</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
@@ -6326,7 +6358,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>A function that inheres in a human being and is realised in processes that enable the human to survive and thrive.</t>
+          <t>An experience-related behaviour that involves avoiding, reducing or escaping anxiety, stress, sorrow, shame and unhappiness.</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -6336,24 +6368,23 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>There are complex sets of processes involved in the realisation of human life functions, only some which would behaviours. An example for a human life function that is not a behaviour function: human thermoregulation via sweating function. However, some behaviours can fulfil 'human life functions'.
-The term 'survive' refers to continuing one's existence (e.g., staying alive), while 'thrive' includes a wide range of processes that improve an animal's life, including physical and mental wellbeing and experiencing positive social interactions, as well as being able to reproduce. Many processes can contribute to a human surviving and thriving.</t>
+          <t>distress minimization behaviour</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BCIO:036107</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>process aggregate</t>
-        </is>
-      </c>
+          <t>BCIO:050834</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>regulatory behaviour</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
@@ -6361,7 +6392,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>An occurrent consisting exactly of a plurality of processes that are process_aggregate_member_parts_of that occurrent for all times at which it exists.</t>
+          <t>An experience-related behaviour that involves monitoring and acting upon some parts of the person or their environment.</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -6369,33 +6400,33 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>Processes that repeat over time.</t>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Environment here includes the social and physical environment and includes behaviours involved in monitoring of others or self, action planning, and goal setting.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BCIO:034000</t>
+          <t>BCIO:050811</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>population behaviour</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>cue management behaviour</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>An aggregate of individual human behaviours of members of a population.</t>
+          <t>A regulatory behaviour in which cues that prompt a behaviour pattern are added, altered or removed.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -6407,14 +6438,14 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BCIO:050808</t>
+          <t>BCIO:050841</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>collective behaviour</t>
+          <t>approach behaviour</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -6424,7 +6455,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>A population behaviour that is aimed at achieving a goal shared by members of that population.</t>
+          <t>An experience-related behaviour that involves taking action to engage with some stimulus that is judged to be rewarding by the person.</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -6436,16 +6467,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BCIO:050267</t>
+          <t>BCIO:036030</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>uniform process aggregate</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>sexual behaviour</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
@@ -6453,7 +6484,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>A process aggregate whose member parts are of the same type.</t>
+          <t>An experience-related behaviour that involves sexual arousal.</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -6461,23 +6492,23 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>Several processes of the same type repeated over time.</t>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>The classes 'reproductive behaviour' and 'sexual behaviour' have some instances in which they would overlap. For instance, a subclass of both of these classes would be 'reproductive sexual behaviour'. Examples for 'reproductive sexual behaviour' can be annotated by using the two classes: 'reproductive behaviour' and 'sexual behaviour'. There are also various examples in which the classes 'reproductive behaviour' does not overlap with sexual behaviour. For instance, fertility preservation would be a reproductive behaviour but not a sexual behaviour. Similarly, various sexual behaviours do not have a reproductive function. For instance, performing oral sex may not have a reproductive function.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BCIO:036100</t>
+          <t>BCIO:036073</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>individual human behaviour pattern</t>
+          <t>avoidance behaviour</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -6487,52 +6518,36 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>A uniform process aggregate whose member parts are behaviours of the same type and in the same person.</t>
+          <t>An experience-related behaviour that involves taking defensive action in order to avoid some stimulus judged to be aversive by the person.</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>Individual human behaviours of the same type repeated over time.</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>The term 'pattern' is used to refer to several processes (individual human behaviours) of the same type being repeated overtime.
-This class is intended to include behaviours that can usefully be characterised in terms of frequency and pattern of enactment with a temporal start and end of the series. This means that the series can be terminated (e.g. stopping smoking), interrupted (e.g. abstaining from alcohol consumption for a month), and changed in frequency (e.g. cutting down on snacks).</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>behaviour pattern</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BCIO:050210</t>
+          <t>BCIO:036112</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>consumption behaviour pattern</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>spiritual behaviour</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>An individual human behaviour pattern that involves consumption behaviour.</t>
+          <t>An experience-related behaviour that is performed in line with a belief system that is grounded in reverence for a supernatural power or powers and provides meaning in life.</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -6544,24 +6559,24 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BCIO:050211</t>
+          <t>BCIO:036041</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>mind-body behaviour</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>substance use behaviour pattern</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>A consumption behaviour pattern that involves substance use behaviour.</t>
+          <t>An experience-related behaviour that aims to create a sense of interconnectedness between the mind and the body.</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -6573,135 +6588,125 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BCIO:036102</t>
+          <t>BCIO:036047</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>enjoyment behaviour</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>tobacco use behaviour pattern</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>A substance use behaviour pattern that involves tobacco use.</t>
+          <t>An experience-related behaviour that is performed to experience pleasure or satisfaction.</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>tobacco use</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BCIO:036104</t>
+          <t>BCIO:006158</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>habitual behaviour</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>tobacco smoking behaviour pattern</t>
-        </is>
-      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>A tobacco use behaviour pattern that involves tobacco smoking behaviour.</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>behaviour</t>
+          <t>An &lt;individual human behaviour&gt; that results from a learnt stimulus-behaviour co-occurrence.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BCIO:036106</t>
+          <t>BCIO:050809</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>coping behaviour</t>
+        </is>
+      </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>cigarette smoking behaviour pattern</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>A tobacco smoking behaviour pattern that involves cigarette smoking behaviour.</t>
+          <t>An individual human behaviour that has the goal to reduce harm or discomfort.</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>behaviour</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BCIO:050805</t>
+          <t>BCIO:050438</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>life function-related behaviour</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>behaviour pattern maintenance</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>An individual human behaviour pattern that is continued.</t>
+          <t>An individual human behaviour related to vital bodily functions.</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>Behaviour is continued even if there are historical or current barriers to doing so.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BCIO:050448</t>
+          <t>BCIO:036057</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>population behaviour pattern</t>
+          <t>breathing behaviour</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6711,7 +6716,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>A uniform process aggregate whose members are individual behaviour patterns of a population.</t>
+          <t>A life function-related behaviour involves providing an appropriate level of oxygenation to body tissues.</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -6723,16 +6728,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BCIO:050804</t>
+          <t>BCIO:036054</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>behaviour chain</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>excretion behaviour</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
@@ -6740,33 +6745,28 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>A process aggregate whose members are behaviours causally linked to each other in a sequence.</t>
+          <t>A life function-related behaviour that involves eliminating excess or harmful chemicals produced by bodily functions.</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>A behaviour chain can involve different behaviours, whereas a behaviour pattern can involve the same behaviour. Patterns are not necessarily causally linked.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BCIO:006085</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
+          <t>BCIO:036056</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>reproductive behaviour</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
@@ -6774,34 +6774,29 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>A spatial &lt;quality&gt; that inheres in a bearer by virtue of its position relative to other entities.</t>
+          <t>A life function-related behaviour that involves producing offspring based on combining DNA of two or more people.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Mechanisms of action</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>Where a person, animal or object is.</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>An intervention could be used to rearrange objects in an environment, changing the location of a person relative to these objects and thereby increasing the likelihood of a behaviour.</t>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>The classes 'reproductive behaviour' and 'sexual behaviour' have some instances in which they would overlap. For instance, a subclass of both of these classes would be 'reproductive sexual behaviour'. Examples for 'reproductive sexual behaviour' can be annotated by using the two classes: 'reproductive behaviour' and 'sexual behaviour'. There are also various examples in which the classes 'reproductive behaviour' does not overlap with sexual behaviour. For instance, fertility preservation would be a reproductive behaviour but not a sexual behaviour. Similarly, various sexual behaviours do not have a reproductive function. For instance, performing oral sex may not have a reproductive function.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BCIO:050429</t>
+          <t>BCIO:050416</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>number of behavioural occurrences</t>
+          <t>behavioural disposition</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -6813,7 +6808,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times a behaviour has occurred.</t>
+          <t>A bodily disposition that is realised as some behaviour.</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -6821,21 +6816,21 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of times a person performs a behaviour. </t>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>A tendency to behave in a particular way.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BCIO:050428</t>
+          <t>BCIO:050450</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>behavioural frequency</t>
+          <t>abstinence end point</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -6847,7 +6842,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times a behaviour occurs in a time period.</t>
+          <t>A temporal region when a person stops abstaining from a behaviour.</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -6855,21 +6850,26 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>The number of times a person performs a behaviour within a specific period.</t>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>A time point that is the end of an abstinence period.</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BCIO:050300</t>
+          <t>BCIO:050453</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>personal attribute</t>
+          <t>behaviour end point</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -6881,32 +6881,37 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant that inheres in a person.</t>
+          <t>A time point that is the end of an individual human behaviour.</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attributes included under this header are age, immigration, social and economic conditions. </t>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>A temporal region when a behaviour ends.</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BCIO:050451</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>abstinence from a behaviour</t>
-        </is>
-      </c>
+          <t>BCIO:050454</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>behaviour starting point</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
@@ -6915,7 +6920,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>A personal attribute in which a person does not engage in a behaviour during a time period.</t>
+          <t>A time point that is the start of an individual human behaviour.</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -6923,21 +6928,26 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>Not performing a behaviour for some period of time.</t>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>A temporal region when a behaviour starts.</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BCIO:050453</t>
+          <t>BCIO:050452</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>behaviour end point</t>
+          <t>abstinence start point</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -6949,7 +6959,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>A time point that is the end of an individual human behaviour.</t>
+          <t>A time point that is the start of an abstinence period.</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -6957,12 +6967,12 @@
           <t>behaviour</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>A temporal region when a behaviour ends.</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>A temporal region when a person starts being abstinent from a behaviour.</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
         <is>
           <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
         </is>
@@ -6971,12 +6981,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BCIO:050454</t>
+          <t>BCIO:050830</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>behaviour starting point</t>
+          <t>reducing discomfort</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -6988,7 +6998,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>A time point that is the start of an individual human behaviour.</t>
+          <t>A process in which physical or mental uneasiness or distress is reduced.</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -6998,24 +7008,19 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>A temporal region when a behaviour starts.</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
+          <t>distress minimisation behaviour</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BCIO:050450</t>
+          <t>BCIO:050831</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>abstinence end point</t>
+          <t>reducing harm</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -7027,7 +7032,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>A temporal region when a person stops abstaining from a behaviour.</t>
+          <t>A process in which damage or injury is reduced.</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -7037,24 +7042,19 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>A time point that is the end of an abstinence period.</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
+          <t>harmful behaviour</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BCIO:050452</t>
+          <t>BCIO:042000</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>abstinence start point</t>
+          <t>human behaviour</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -7066,37 +7066,27 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>A time point that is the start of an abstinence period.</t>
+          <t>A process that is an individual human behaviour or a population behaviour.</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>A temporal region when a person starts being abstinent from a behaviour.</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence. </t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BCIO:050806</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>behavioural consequence</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>BCIO:002000</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>behaviour change intervention outcome behaviour</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
@@ -7105,27 +7095,22 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>An entity that is an outcome of behaviour.</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>behaviour</t>
+          <t>Human behaviour that is an intervention outcome.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BCIO:050919</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>negative behavioural consequence</t>
-        </is>
-      </c>
+          <t>BCIO:050209</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>individual human behaviour change</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
@@ -7134,20 +7119,40 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>A behavioural consequence that is negatively evaluated by an individual or a population.</t>
+          <t>A process that results in a difference in enactment of some individual human behaviour or individual human behaviour pattern from what would have been the case otherwise.</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Changing a behaviour or behaviour pattern from what would have happened otherwise.</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>behaviour change</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>The term 'change' in behaviour change refers to change from what would have happened in the absence of a causal process. Thus. a process that results in a behaviour (e.g. going to the gym) being maintained when otherwise it would have lapsed is included in the class, as is not taking up smoking as a result of some intervention. behaviour change can refer to individual behaviours (e.g. attending a breast cancer screening appointment) or behaviour patterns (e.g. regular consumption of alcoholic beverages).</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BCIO:050900</t>
+          <t>BCIO:050575</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>social behavioural consequence</t>
+          <t>behaviour change through group norm</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -7158,7 +7163,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>A behavioural consequence of a member of the person’s social environmental system.</t>
+          <t>An &lt;individual human behaviour change&gt; resulting from exposure to a group behavioural norm.</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -7170,16 +7175,16 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BCIO:050899</t>
+          <t>BCIO:050207</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>family behavioural consequence</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>individual human behaviour pattern cessation</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
@@ -7187,26 +7192,36 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>A social behavioural consequence of some family member.</t>
+          <t>Individual human behaviour change that involves a person, who enacted a behaviour pattern until a specific timepoint, not performing this behaviour for a duration after that specific timepoint.</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Having stopped engaging in a behaviour pattern for a period of time.</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>behavioural cessation; cessation of a behaviour pattern</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BCIO:050901</t>
+          <t>BCIO:050208</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>wider community behavioural consequence</t>
+          <t>tobacco use cessation</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -7216,36 +7231,47 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>A social behavioural consequence that is beyond the person’s family.</t>
+          <t>Individual human behaviour pattern cessation in which the behaviour pattern is tobacco use.</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Cessation of tobacco use for a period of time.</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As with the parent class 'individual human behaviour pattern cessation'  this class can only be identified after the duration for which cessation has occurred has elapsed and it is necessary to specify this period for the class to be meaningful.
+</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BCIO:050828</t>
+          <t>BCIO:050269</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>positive behavioural consequence</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>tobacco smoking cessation</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>A behavioural consequence that is positively evaluated by an individual or a population.</t>
+          <t>Tobacco use cessation in which the form of tobacco use is tobacco smoking.</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -7257,24 +7283,24 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BCIO:050820</t>
+          <t>BCIO:050311</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>harm prevention</t>
-        </is>
-      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>cigarette smoking cessation</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>A behavioural consequence in which harm is prevented.</t>
+          <t>Tobacco smoking cessation in which the form of tobacco smoking is cigarette smoking.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -7286,15 +7312,15 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BCIO:050823</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>impact of behaviour on environment</t>
-        </is>
-      </c>
+          <t>BCIO:050806</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>behavioural consequence</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
@@ -7303,7 +7329,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>A behavioural consequence that involves an outcome relating to the environment system.</t>
+          <t>An entity that is an outcome of behaviour.</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -7315,15 +7341,15 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BCIO:050830</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>reducing discomfort</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
+          <t>BCIO:050900</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>social behavioural consequence</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
@@ -7332,33 +7358,28 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>A process in which physical or mental uneasiness or distress is reduced.</t>
+          <t>A behavioural consequence of a member of the person’s social environmental system.</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>distress minimisation behaviour</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BCIO:050831</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>reducing harm</t>
-        </is>
-      </c>
+          <t>BCIO:050901</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>wider community behavioural consequence</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
@@ -7366,33 +7387,28 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>A process in which damage or injury is reduced.</t>
+          <t>A social behavioural consequence that is beyond the person’s family.</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>harmful behaviour</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BCIO:050209</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>individual human behaviour change</t>
-        </is>
-      </c>
+          <t>BCIO:050899</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>family behavioural consequence</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
@@ -7400,40 +7416,25 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>A process that results in a difference in enactment of some individual human behaviour or individual human behaviour pattern from what would have been the case otherwise.</t>
+          <t>A social behavioural consequence of some family member.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>Changing a behaviour or behaviour pattern from what would have happened otherwise.</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>The term 'change' in behaviour change refers to change from what would have happened in the absence of a causal process. Thus. a process that results in a behaviour (e.g. going to the gym) being maintained when otherwise it would have lapsed is included in the class, as is not taking up smoking as a result of some intervention. behaviour change can refer to individual behaviours (e.g. attending a breast cancer screening appointment) or behaviour patterns (e.g. regular consumption of alcoholic beverages).</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>behaviour change</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BCIO:050575</t>
+          <t>BCIO:050919</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>behaviour change through group norm</t>
+          <t>negative behavioural consequence</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -7444,25 +7445,20 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>An &lt;individual human behaviour change&gt; resulting from exposure to a group behavioural norm.</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>behaviour</t>
+          <t>A behavioural consequence that is negatively evaluated by an individual or a population.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BCIO:050207</t>
+          <t>BCIO:050820</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>individual human behaviour pattern cessation</t>
+          <t>harm prevention</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -7473,38 +7469,28 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Individual human behaviour change that involves a person, who enacted a behaviour pattern until a specific timepoint, not performing this behaviour for a duration after that specific timepoint.</t>
+          <t>A behavioural consequence in which harm is prevented.</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>Having stopped engaging in a behaviour pattern for a period of time.</t>
-        </is>
-      </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>behavioural cessation; cessation of a behaviour pattern</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BCIO:050208</t>
+          <t>BCIO:050828</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>tobacco use cessation</t>
-        </is>
-      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>positive behavioural consequence</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
@@ -7512,47 +7498,36 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Individual human behaviour pattern cessation in which the behaviour pattern is tobacco use.</t>
+          <t>A behavioural consequence that is positively evaluated by an individual or a population.</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
           <t>behaviour</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Cessation of tobacco use for a period of time.</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As with the parent class 'individual human behaviour pattern cessation'  this class can only be identified after the duration for which cessation has occurred has elapsed and it is necessary to specify this period for the class to be meaningful.
-</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BCIO:050269</t>
+          <t>BCIO:050823</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>impact of behaviour on environment</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>tobacco smoking cessation</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Tobacco use cessation in which the form of tobacco use is tobacco smoking.</t>
+          <t>A behavioural consequence that involves an outcome relating to the environment system.</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -7564,41 +7539,51 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BCIO:050311</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
+          <t>BCIO:006085</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>cigarette smoking cessation</t>
-        </is>
-      </c>
+      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Tobacco smoking cessation in which the form of tobacco smoking is cigarette smoking.</t>
+          <t>A spatial &lt;quality&gt; that inheres in a bearer by virtue of its position relative to other entities.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>behaviour</t>
+          <t>Mechanisms of action</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Where a person, animal or object is.</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>An intervention could be used to rearrange objects in an environment, changing the location of a person relative to these objects and thereby increasing the likelihood of a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BCIO:042000</t>
+          <t>BCIO:050455</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>human behaviour</t>
+          <t>behavioural duration</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -7610,27 +7595,32 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>A process that is an individual human behaviour or a population behaviour.</t>
+          <t>A temporal interval within which an individual human behaviour occurs.</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
           <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>The time between the start and end of a behaviour.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BCIO:002000</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>behaviour change intervention outcome behaviour</t>
-        </is>
-      </c>
+          <t>BCIO:050449</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>abstinence duration</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
@@ -7639,7 +7629,17 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Human behaviour that is an intervention outcome.</t>
+          <t>A temporal interval during which a person is abstinent from a behaviour.</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>The time a person is abstinent from a behaviour.</t>
         </is>
       </c>
     </row>

--- a/Behaviour/BCIO-behaviour-hierarchy.xlsx
+++ b/Behaviour/BCIO-behaviour-hierarchy.xlsx
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>spécification d’intervalle de dose</t>
+          <t>dose range specification</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -598,7 +598,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>An information content entity that specifies the minimum and maximum quantities of drug product or active ingredient in a dose administration.</t>
+          <t>Une entité de contenu informationnel qui spécifie les quantités minimum et maximum de médicament ou d’ingrédient actif dans une administration de dose.</t>
         </is>
       </c>
     </row>
@@ -15991,7 +15991,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>BCIO:015392</t>
+          <t>BCIO:015317</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -16001,7 +16001,7 @@
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr">
         <is>
-          <t>history of exposure to an occupational hazard population statistic</t>
+          <t>expertise discipline population statistic</t>
         </is>
       </c>
       <c r="H598" t="inlineStr"/>
@@ -16010,14 +16010,14 @@
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr">
         <is>
-          <t>A population statistic about history of exposure to an occupational hazard.</t>
+          <t>A population statistic about expertise discipline.</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>BCIO:015393</t>
+          <t>BCIO:015287</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -16028,7 +16028,7 @@
       <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr">
         <is>
-          <t>percentage history of exposure to an occupational hazard population statistic</t>
+          <t>discipline of current programme of study or training population statistic</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
@@ -16036,14 +16036,14 @@
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A population statistic about discipline of current programme of study or training.</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>BCIO:015394</t>
+          <t>BCIO:015288</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -16052,24 +16052,24 @@
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr"/>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>proportion history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="I600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>percentage discipline of current programme of study or training population statistic</t>
+        </is>
+      </c>
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A(n) discipline of current programme of study or training population statistic that is the percentage of people that have a discipline of current programme of study or training in the population.</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>BCIO:015317</t>
+          <t>BCIO:015289</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -16077,25 +16077,25 @@
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>expertise discipline population statistic</t>
-        </is>
-      </c>
+      <c r="G601" t="inlineStr"/>
       <c r="H601" t="inlineStr"/>
-      <c r="I601" t="inlineStr"/>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>proportion discipline of current programme of study or training population statistic</t>
+        </is>
+      </c>
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
         <is>
-          <t>A population statistic about expertise discipline.</t>
+          <t>A(n) discipline of current programme of study or training population statistic that is the proportion of people that have a discipline of current programme of study or training in the population.</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>BCIO:015287</t>
+          <t>BCIO:015319</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -16106,7 +16106,7 @@
       <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training population statistic</t>
+          <t>proportion expertise discipline population statistic</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
@@ -16114,14 +16114,14 @@
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
-          <t>A population statistic about discipline of current programme of study or training.</t>
+          <t>A(n) expertise discipline population statistic that is the proportion of people that have a expertise discipline in the population.</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>BCIO:015288</t>
+          <t>BCIO:015318</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -16130,24 +16130,24 @@
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr"/>
       <c r="G603" t="inlineStr"/>
-      <c r="H603" t="inlineStr"/>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>percentage discipline of current programme of study or training population statistic</t>
-        </is>
-      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>percentage expertise discipline population statistic</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
-          <t>A(n) discipline of current programme of study or training population statistic that is the percentage of people that have a discipline of current programme of study or training in the population.</t>
+          <t>A(n) expertise discipline population statistic that is the percentage of people that have a expertise discipline in the population.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BCIO:015289</t>
+          <t>BCIO:015290</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -16156,24 +16156,24 @@
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr"/>
-      <c r="H604" t="inlineStr"/>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>proportion discipline of current programme of study or training population statistic</t>
-        </is>
-      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr"/>
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
-          <t>A(n) discipline of current programme of study or training population statistic that is the proportion of people that have a discipline of current programme of study or training in the population.</t>
+          <t>A population statistic about discipline of highest level of formal educational qualification achieved.</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>BCIO:015319</t>
+          <t>BCIO:015292</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -16182,24 +16182,24 @@
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr"/>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>proportion expertise discipline population statistic</t>
-        </is>
-      </c>
-      <c r="I605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>proportion discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
-          <t>A(n) expertise discipline population statistic that is the proportion of people that have a expertise discipline in the population.</t>
+          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the proportion of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BCIO:015318</t>
+          <t>BCIO:015291</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -16208,24 +16208,24 @@
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr"/>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>percentage expertise discipline population statistic</t>
-        </is>
-      </c>
-      <c r="I606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>percentage discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
-          <t>A(n) expertise discipline population statistic that is the percentage of people that have a expertise discipline in the population.</t>
+          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the percentage of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>BCIO:015290</t>
+          <t>BCIO:015392</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -16233,25 +16233,25 @@
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr"/>
-      <c r="H607" t="inlineStr">
-        <is>
-          <t>discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr"/>
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
-          <t>A population statistic about discipline of highest level of formal educational qualification achieved.</t>
+          <t>A population statistic about history of exposure to an occupational hazard.</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>BCIO:015292</t>
+          <t>BCIO:015393</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -16260,24 +16260,24 @@
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr"/>
-      <c r="H608" t="inlineStr"/>
-      <c r="I608" t="inlineStr">
-        <is>
-          <t>proportion discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>percentage history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr"/>
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr">
         <is>
-          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the proportion of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>BCIO:015291</t>
+          <t>BCIO:015394</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -16286,17 +16286,17 @@
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr"/>
-      <c r="H609" t="inlineStr"/>
-      <c r="I609" t="inlineStr">
-        <is>
-          <t>percentage discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>proportion history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr"/>
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr">
         <is>
-          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the percentage of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20649,7 @@
       <c r="K777" t="inlineStr"/>
       <c r="L777" t="inlineStr">
         <is>
-          <t>A person between 13 and 19 years of age.</t>
+          <t>A person who is between the ages of  13 and 19.</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       <c r="D828" t="inlineStr"/>
       <c r="E828" t="inlineStr">
         <is>
-          <t>fiat object</t>
+          <t>fiat object part</t>
         </is>
       </c>
       <c r="F828" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       <c r="K838" t="inlineStr"/>
       <c r="L838" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="E840" t="inlineStr"/>
@@ -22486,7 +22486,7 @@
       <c r="K848" t="inlineStr"/>
       <c r="L848" t="inlineStr">
         <is>
-          <t>A bodily disposition is a disposition that inheres in some extended organism. Examples are: my disposition to catch a cold when exposed to a virus, my ability to speak the English language.</t>
+          <t>A disposition that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22886,7 @@
       <c r="K863" t="inlineStr"/>
       <c r="L863" t="inlineStr">
         <is>
-          <t>A bodily disposition that is realized in a mental process.</t>
+          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
         </is>
       </c>
     </row>
@@ -39444,7 +39444,7 @@
       <c r="K1409" t="inlineStr"/>
       <c r="L1409" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -45932,7 +45932,7 @@
       <c r="K1616" t="inlineStr"/>
       <c r="L1616" t="inlineStr">
         <is>
-          <t>An &lt;affective process&gt; that involves the experience of internal or external sensory stimuli.</t>
+          <t>The subjective emotional feeling is that (fiat) part of the emotion process by which the organism experiences its own emotion.</t>
         </is>
       </c>
     </row>
